--- a/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,441 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 겁이 나서 오게 된 이유는요... 직장에서, 감시실이 조용해지는 시간대에, 모니터 스피커를 통해 목소리를 듣고 있어서예요. "루스, 너 그거 놓쳤어"라거나 "너 때문에 사람들이 다칠 거야" 같은 말을 해요.
+근데 문제는, 채널이 음소거돼 있다는 거예요. 그리고 다른 사람은 아무도 못 들어요. 정말 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 들리는 목소리가 뭔가를 하라고 시킨 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 명령처럼 정확히 그런 건 아니에요. 그보다는 저를 비난하거나 경고하는 느낌이에요—"루스, 너 그거 놓쳤어" 아니면 "너 때문에 사람들이 다칠 거야" 같은 거요. 모든 게 음소거돼 있을 때도 모니터 스피커를 통해서 들리고, 다른 사람은 아무것도 못 듣는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 목소리는 감시실에 있을 때만 들리나요, 아니면 다른 시간이나 장소에서도 들리나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 지금까지는 정말 감시실에서만이에요, 조용해지는 시간대에요. 모니터 스피커를 통해 들려오는 것처럼 느껴져요, 채널이 음소거돼 있어도요. 다른 곳에서는 딱히 겪은 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 기분이 자주 또는 예상치 못하게 바뀐다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 갑자기 바뀐다고는 말 못 하겠어요. 그런 급격한 기분 변화는 딱히 못 느꼈어요. 대부분 그냥 같은 낮은 상태에 갇혀 있는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 목소리가 주는 비난이나 경고가 사실이라고 믿으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 제 일부는 정말로 그걸 믿어요, 네. 놓쳤던 카메라 앵글이나 늦게 처리했던 통화들을 계속 되짚어보게 되는데, 그게 제가 부주의하다는... 심지어 위험하다는 증거처럼 느껴져요. 그리고 제가 근무하는 동안 뭔가 잘못되면, 저는 그 벌을 받아 마땅하다고 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 오랫동안 극도로 가라앉거나 우울한 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 대부분의 날에는 침대에서 일어나기도 전에 이미 이 무거운 회색빛 기분을 안고 눈을 뜨는 느낌이에요. 꽤 오래 이어졌어요. 가끔은 근무 전에 차 안에 앉아 있다가 카지노 조명을 보기만 해도 뚜렷한 이유 없이 눈물이 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 극도로 들뜨거나 비정상적으로 활력이 넘쳤던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 그렇게 비정상적으로 들뜨거나 에너지가 넘쳤던 시기는 기억이 안 나요. 오히려 제 에너지는 낮은 편이었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 극도로 짜증이 났던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 그런 시기 전체는 없었던 것 같아요. 가끔 답답해지긴 하는데, 극도로 짜증이 나거나 며칠씩 그게 지배하는 정도는 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 극도로 행복하거나 세상 꼭대기에 있는 것 같은 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 딱히 없어요. 그렇게 세상 꼭대기에 있거나 비정상적으로 행복했던 시기는 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 다른 사람들이 아니라고 말해도, 목소리가 암시하는 것처럼 자신이 부주의하거나 위험하다는 믿음이 사실이라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네... 많은 경우 그래요. 누군가 제가 부주의하지 않다고 말해줘도, 놓쳤던 카메라 앵글이나 늦게 처리했던 통화를 계속 되짚어보게 되고, 그게 제가 일에서 위험하다는 증거처럼 느껴져요. 제 일부는 정말로 제가 감시하는 동안 뭔가 잘못되면 벌을 받아 마땅하다고 믿어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 낮은 기분 때문에 일상 활동이나 업무를 하기 힘드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 일이 더 힘들어졌어요. 이미 근무 서류에서 실수를 했고, 예전처럼 따라갈 수가 없어서 활동이나 친구들 만나는 것에서 좀 물러나야 했어요.
+집에서는 대부분 기본적인 것만 하고 있어요. 요리도 별로 안 하고, 사람들을 초대하지도 않고, 예전에 챙기던 일들도 잘 못 챙기고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 비정상적으로 자신감이 넘치거나 낙관적이었던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 제 자신에게 괜찮을 거라고 말해보려던 시기는 있었지만, 비정상적으로 자신감이 넘치거나 낙관적으로 느껴진 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 잠을 많이 자지 않아도 개운함을 느꼈던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 잠을 많이 못 자면 보통 지치기만 해요, 개운하거나 활력 넘치는 게 아니라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 비정상적으로 활력이 넘치고 잠을 많이 필요로 하지 않았던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 아니요, 그런 시기는 없었어요. 잠을 못 자면 활력이 넘치는 게 아니라—그냥 피곤할 뿐이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 낮은 기분이 눈에 띄게 나아졌던 시기가 있었나요, 잠깐이라도요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 딱히 없었어요. 대부분의 날에는 침대에서 일어나기도 전에 이 무거운 회색빛 느낌이 이미 있어요. 근무 가는 길에 카지노 조명을 보기만 해도 눈물이 나고, 딱히 뚜렷한 이유도 없어요. 잘 나아지지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 낮은 기분이 하루 이상 나아진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 아니요, 딱히 하루 이상은 없어요. 대부분의 날에는 침대에서 일어나기도 전에 그 무거운 회색빛 기분이 이미 있어요. 근무 전에 카지노 조명을 보기만 해도 뚜렷한 이유 없이 눈물이 나기도 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 목소리와 부주의하다는 믿음이 현실에 근거하지 않았을 가능성이 있다고 생각해보신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 모르겠어요. 제 일부는 선생님이 하시는 말씀을 이해할 수 있어요, 어쩌면 제 마음이 상황을 더 나쁘게 만들고 있을지도 모른다는 거요. 근데 일에 대해 생각하면, 놓쳤던 카메라 앵글이나 늦게 처리했던 통화들을 계속 되짚어보게 되고, 그게 제가 부주의하다는... 위험하다는 증거처럼 느껴져요. 그리고 제가 근무하는 동안 뭔가 잘못되면, 제 일부는 정말로 벌을 받아 마땅하다고 믿어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 말씀하신 이 무거운 회색빛 기분을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 이제 넉 달 정도 됐어요. 카지노에서 감시 책임자 역할로 옮겨진 이후부터 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 들리는 목소리들이 시작된 이후로 몇 주 정도라도 멈춘 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 아니요, 몇 주씩은 없었어요. 책임자로 자리를 옮긴 이후 이렇게 절망적이고 죄책감을 느끼기 시작한 이 시기와 함께 시작됐어요. 그전에는 장비를 통해 비난이 들리거나 제가 모두에게 위험하다고 그렇게 확신했던 적이 없었어요. 다 이 낮은 시기랑 함께 얽혀 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 낮은 기분과 이 무거운 회색빛 느낌이 나아지면 목소리와 부주의하거나 위험하다는 느낌도 사라질 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 그럴 것 같아요, 네. 그러니까, 책임자 역할로 옮겨진 이후 이렇게 절망적이고 죄책감을 느끼는 시기 전에는, 장비를 통해 비난을 들은 적이 없었어요. 제가 모두에게 위험하다고 그렇게 확신하지도 않았고요. 그래서 목소리랑 그런 생각들이 같은 낮은 시기의 일부인 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 주요우울장애 (D015)
 인구통계: 성별 여성 / 나이 44 / 직업상태 security guard or gambling surveillance officer / 최종학력 학사
@@ -575,499 +1001,41 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the major depressive episode
 주호소 증상 코드: S020
-배경 서술: 인력 개편 이후 익숙했던 층 순찰 업무에서 카지노 감시 책임자 역할로 자리를 옮기게 되었을 때, 루스는 처음에는 다른 규정 변경들처럼 대수롭지 않게 받아들이고 CCTV 관제실에서 사기를 북돋우려 애썼다. 그 후 넉 달에 걸쳐, 사건들을 검토하고 영상 시스템을 문제 해결하며 다른 경비원들의 결정에 대한 책임까지 지는 부담이 점차 그녀의 삶을 좁혀갔다: 그녀는 살사 수업과 소프트볼 연습에 나가지 않게 되었고, 업무 중에는 행동이 느려졌으며, 퇴근 후에는 너무 지쳐서 요리도, PC 조립도, 보드게임 모임도 열 수 없었다. 그녀의 기분은 지속적으로 절망적이 되었고, 그녀의 책임감은 놓친 카메라 앵글 하나하나에 대한 과도한 죄책감으로 변했으며, 아무도 말하지 않는데도 모니터 화면 너머로 분명한 비난의 소리를 듣기 시작했고, 자신이 사라지면 모두가 더 안전할 거라는 반복적인 생각도 동반했다. 근무 보고에서 아슬아슬한 사고가 있었고 카지노 직원 지원 상담사에게 눈물을 흘리며 털어놓은 후, 그녀는 정신과 평가에 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 겁이 나서 오게 된 이유는요... 직장에서, 감시실이 조용해지는 시간대에, 모니터 스피커를 통해 목소리를 듣고 있어서예요. "루스, 너 그거 놓쳤어"라거나 "너 때문에 사람들이 다칠 거야" 같은 말을 해요.
-근데 문제는, 채널이 음소거돼 있다는 거예요. 그리고 다른 사람은 아무도 못 들어요. 정말 무서워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 들리는 목소리가 뭔가를 하라고 시킨 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 명령처럼 정확히 그런 건 아니에요. 그보다는 저를 비난하거나 경고하는 느낌이에요—"루스, 너 그거 놓쳤어" 아니면 "너 때문에 사람들이 다칠 거야" 같은 거요. 모든 게 음소거돼 있을 때도 모니터 스피커를 통해서 들리고, 다른 사람은 아무것도 못 듣는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 목소리는 감시실에 있을 때만 들리나요, 아니면 다른 시간이나 장소에서도 들리나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 지금까지는 정말 감시실에서만이에요, 조용해지는 시간대에요. 모니터 스피커를 통해 들려오는 것처럼 느껴져요, 채널이 음소거돼 있어도요. 다른 곳에서는 딱히 겪은 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 기분이 자주 또는 예상치 못하게 바뀐다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 갑자기 바뀐다고는 말 못 하겠어요. 그런 급격한 기분 변화는 딱히 못 느꼈어요. 대부분 그냥 같은 낮은 상태에 갇혀 있는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 목소리가 주는 비난이나 경고가 사실이라고 믿으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 제 일부는 정말로 그걸 믿어요, 네. 놓쳤던 카메라 앵글이나 늦게 처리했던 통화들을 계속 되짚어보게 되는데, 그게 제가 부주의하다는... 심지어 위험하다는 증거처럼 느껴져요. 그리고 제가 근무하는 동안 뭔가 잘못되면, 저는 그 벌을 받아 마땅하다고 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 오랫동안 극도로 가라앉거나 우울한 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 대부분의 날에는 침대에서 일어나기도 전에 이미 이 무거운 회색빛 기분을 안고 눈을 뜨는 느낌이에요. 꽤 오래 이어졌어요. 가끔은 근무 전에 차 안에 앉아 있다가 카지노 조명을 보기만 해도 뚜렷한 이유 없이 눈물이 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 극도로 들뜨거나 비정상적으로 활력이 넘쳤던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 그렇게 비정상적으로 들뜨거나 에너지가 넘쳤던 시기는 기억이 안 나요. 오히려 제 에너지는 낮은 편이었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 극도로 짜증이 났던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 그런 시기 전체는 없었던 것 같아요. 가끔 답답해지긴 하는데, 극도로 짜증이 나거나 며칠씩 그게 지배하는 정도는 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 극도로 행복하거나 세상 꼭대기에 있는 것 같은 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 딱히 없어요. 그렇게 세상 꼭대기에 있거나 비정상적으로 행복했던 시기는 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 다른 사람들이 아니라고 말해도, 목소리가 암시하는 것처럼 자신이 부주의하거나 위험하다는 믿음이 사실이라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네... 많은 경우 그래요. 누군가 제가 부주의하지 않다고 말해줘도, 놓쳤던 카메라 앵글이나 늦게 처리했던 통화를 계속 되짚어보게 되고, 그게 제가 일에서 위험하다는 증거처럼 느껴져요. 제 일부는 정말로 제가 감시하는 동안 뭔가 잘못되면 벌을 받아 마땅하다고 믿어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 낮은 기분 때문에 일상 활동이나 업무를 하기 힘드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 일이 더 힘들어졌어요. 이미 근무 서류에서 실수를 했고, 예전처럼 따라갈 수가 없어서 활동이나 친구들 만나는 것에서 좀 물러나야 했어요.
-집에서는 대부분 기본적인 것만 하고 있어요. 요리도 별로 안 하고, 사람들을 초대하지도 않고, 예전에 챙기던 일들도 잘 못 챙기고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 비정상적으로 자신감이 넘치거나 낙관적이었던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 제 자신에게 괜찮을 거라고 말해보려던 시기는 있었지만, 비정상적으로 자신감이 넘치거나 낙관적으로 느껴진 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 잠을 많이 자지 않아도 개운함을 느꼈던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 잠을 많이 못 자면 보통 지치기만 해요, 개운하거나 활력 넘치는 게 아니라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 비정상적으로 활력이 넘치고 잠을 많이 필요로 하지 않았던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 아니요, 그런 시기는 없었어요. 잠을 못 자면 활력이 넘치는 게 아니라—그냥 피곤할 뿐이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 낮은 기분이 눈에 띄게 나아졌던 시기가 있었나요, 잠깐이라도요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 딱히 없었어요. 대부분의 날에는 침대에서 일어나기도 전에 이 무거운 회색빛 느낌이 이미 있어요. 근무 가는 길에 카지노 조명을 보기만 해도 눈물이 나고, 딱히 뚜렷한 이유도 없어요. 잘 나아지지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 낮은 기분이 하루 이상 나아진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 아니요, 딱히 하루 이상은 없어요. 대부분의 날에는 침대에서 일어나기도 전에 그 무거운 회색빛 기분이 이미 있어요. 근무 전에 카지노 조명을 보기만 해도 뚜렷한 이유 없이 눈물이 나기도 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 목소리와 부주의하다는 믿음이 현실에 근거하지 않았을 가능성이 있다고 생각해보신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 모르겠어요. 제 일부는 선생님이 하시는 말씀을 이해할 수 있어요, 어쩌면 제 마음이 상황을 더 나쁘게 만들고 있을지도 모른다는 거요. 근데 일에 대해 생각하면, 놓쳤던 카메라 앵글이나 늦게 처리했던 통화들을 계속 되짚어보게 되고, 그게 제가 부주의하다는... 위험하다는 증거처럼 느껴져요. 그리고 제가 근무하는 동안 뭔가 잘못되면, 제 일부는 정말로 벌을 받아 마땅하다고 믿어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 말씀하신 이 무거운 회색빛 기분을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 이제 넉 달 정도 됐어요. 카지노에서 감시 책임자 역할로 옮겨진 이후부터 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 들리는 목소리들이 시작된 이후로 몇 주 정도라도 멈춘 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 아니요, 몇 주씩은 없었어요. 책임자로 자리를 옮긴 이후 이렇게 절망적이고 죄책감을 느끼기 시작한 이 시기와 함께 시작됐어요. 그전에는 장비를 통해 비난이 들리거나 제가 모두에게 위험하다고 그렇게 확신했던 적이 없었어요. 다 이 낮은 시기랑 함께 얽혀 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 낮은 기분과 이 무거운 회색빛 느낌이 나아지면 목소리와 부주의하거나 위험하다는 느낌도 사라질 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 그럴 것 같아요, 네. 그러니까, 책임자 역할로 옮겨진 이후 이렇게 절망적이고 죄책감을 느끼는 시기 전에는, 장비를 통해 비난을 들은 적이 없었어요. 제가 모두에게 위험하다고 그렇게 확신하지도 않았고요. 그래서 목소리랑 그런 생각들이 같은 낮은 시기의 일부인 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 인력 개편 이후 익숙했던 층 순찰 업무에서 카지노 감시 책임자 역할로 자리를 옮기게 되었을 때, 루스는 처음에는 다른 규정 변경들처럼 대수롭지 않게 받아들이고 CCTV 관제실에서 사기를 북돋우려 애썼다. 그 후 넉 달에 걸쳐, 사건들을 검토하고 영상 시스템을 문제 해결하며 다른 경비원들의 결정에 대한 책임까지 지는 부담이 점차 그녀의 삶을 좁혀갔다: 그녀는 살사 수업과 소프트볼 연습에 나가지 않게 되었고, 업무 중에는 행동이 느려졌으며, 퇴근 후에는 너무 지쳐서 요리도, PC 조립도, 보드게임 모임도 열 수 없었다. 그녀의 기분은 지속적으로 절망적이 되었고, 그녀의 책임감은 놓친 카메라 앵글 하나하나에 대한 과도한 죄책감으로 변했으며, 아무도 말하지 않는데도 모니터 화면 너머로 분명한 비난의 소리를 듣기 시작했고, 자신이 사라지면 모두가 더 안전할 거라는 반복적인 생각도 동반했다. 근무 보고에서 아슬아슬한 사고가 있었고 카지노 직원 지원 상담사에게 눈물을 흘리며 털어놓은 후, 그녀는 정신과 평가에 의뢰되었다.
+표집된 증상 목록:
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현병 (D005); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -987,6 +987,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1031,11 +1036,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S005_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1566</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1633</v>
+        <v>0.1614</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
